--- a/data/c_vs_random3_checkers.xlsx
+++ b/data/c_vs_random3_checkers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -665,6 +665,116 @@
         <v>29.944</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80</v>
+      </c>
+      <c r="C22" t="n">
+        <v>30.365</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="C23" t="n">
+        <v>30.071</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B24" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>29.828</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="C25" t="n">
+        <v>30.039</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>29.925</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>30.079</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="C28" t="n">
+        <v>30.145</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="C29" t="n">
+        <v>30.176</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80</v>
+      </c>
+      <c r="C30" t="n">
+        <v>29.922</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>30.042</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/c_vs_random3_checkers.xlsx
+++ b/data/c_vs_random3_checkers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,6 +775,193 @@
         <v>30.042</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B32" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="C32" t="n">
+        <v>30.32</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>30.321</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="C34" t="n">
+        <v>30.138</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B35" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="C35" t="n">
+        <v>30.352</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B36" t="n">
+        <v>82</v>
+      </c>
+      <c r="C36" t="n">
+        <v>30.355</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="C37" t="n">
+        <v>30.257</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B38" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>30.236</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B39" t="n">
+        <v>81</v>
+      </c>
+      <c r="C39" t="n">
+        <v>30.164</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B40" t="n">
+        <v>81</v>
+      </c>
+      <c r="C40" t="n">
+        <v>29.714</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="C41" t="n">
+        <v>30.048</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B42" t="n">
+        <v>81</v>
+      </c>
+      <c r="C42" t="n">
+        <v>29.897</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B43" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="C43" t="n">
+        <v>30.388</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="C44" t="n">
+        <v>30.017</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B45" t="n">
+        <v>81</v>
+      </c>
+      <c r="C45" t="n">
+        <v>30.064</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B46" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="C46" t="n">
+        <v>30.226</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B47" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="C47" t="n">
+        <v>30.24</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B48" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="C48" t="n">
+        <v>30.316</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
